--- a/PTBR/Lang/PTBR/Game/GlobalTile.xlsx
+++ b/PTBR/Lang/PTBR/Game/GlobalTile.xlsx
@@ -667,7 +667,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Debaixo do Mar</t>
+          <t>Leito do Mar</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Penhasco Nevado</t>
+          <t>Penhasco</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estrada</t>
+          <t>estrada</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
